--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -666,10 +666,10 @@
     <t>CarePlan.intent</t>
   </si>
   <si>
-    <t>proposal | plan | order | option</t>
-  </si>
-  <si>
-    <t>Indicates the level of authority/intentionality associated with the care plan and where the care plan fits into the workflow chain.</t>
+    <t>Planart</t>
+  </si>
+  <si>
+    <t>Art des Plans – typischerweise plan für den Diagnostikplan.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
@@ -1061,305 +1061,309 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/onko-therapy-goal)
+</t>
+  </si>
+  <si>
+    <t>Diagnoseziel</t>
+  </si>
+  <si>
+    <t>Ziel des Diagnostikplans – z. B. Diagnosesicherung mit Staging und Rezeptorstatus.</t>
+  </si>
+  <si>
+    <t>Goal can be achieving a particular change or merely maintaining a current state or even slowing a decline.</t>
+  </si>
+  <si>
+    <t>Provides context for plan.  Allows plan effectiveness to be evaluated by clinicians.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode&lt;=OBJ].</t>
+  </si>
+  <si>
+    <t>GOL.1</t>
+  </si>
+  <si>
+    <t>CarePlan.activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Diagnostische Maßnahmen</t>
+  </si>
+  <si>
+    <t>Geplante bzw. durchgeführte Schritte des Diagnosepfads.</t>
+  </si>
+  <si>
+    <t>Allows systems to prompt for performance of planned activities, and validate plans against best practice.</t>
+  </si>
+  <si>
+    <t>cpl-3:Provide a reference or detail, not both {detail.empty() or reference.empty()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>{no mapping
+NOTE: This is a list of contained Request-Event tuples!}</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].target</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.outcomeCodeableConcept</t>
+  </si>
+  <si>
+    <t>Results of the activity</t>
+  </si>
+  <si>
+    <t>Identifies the outcome at the point when the status of the activity is assessed.  For example, the outcome of an education activity could be patient understands (or not).</t>
+  </si>
+  <si>
+    <t>Note that this should not duplicate the activity status (e.g. completed or in progress).</t>
+  </si>
+  <si>
+    <t>Identifies the results of the activity.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.outcomeReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DiagnosticReport|Observation|Procedure)
+</t>
+  </si>
+  <si>
+    <t>Ergebnis</t>
+  </si>
+  <si>
+    <t>Referenz auf das Ergebnis der Diagnostik – z. B. DiagnosticReport oder Observation.</t>
+  </si>
+  <si>
+    <t>The activity outcome is independent of the outcome of the related goal(s).  For example, if the goal is to achieve a target body weight of 150 lbs and an activity is defined to diet, then the activity outcome could be calories consumed whereas the goal outcome is an observation for the actual body weight measured.</t>
+  </si>
+  <si>
+    <t>Links plan to resulting actions.</t>
+  </si>
+  <si>
+    <t>{Event that is outcome of Request in activity.reference}</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=FLFS].source</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Comments about the activity status/progress</t>
+  </si>
+  <si>
+    <t>Notes about the adherence/status/progress of the activity.</t>
+  </si>
+  <si>
+    <t>This element should NOT be used to describe the activity to be performed - that occurs either within the resource pointed to by activity.detail.reference or in activity.detail.description.</t>
+  </si>
+  <si>
+    <t>Can be used to capture information about adherence, progress, concerns, etc.</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
+  </si>
+  <si>
+    <t>NTE?</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(ServiceRequest|Appointment|Task)
+</t>
+  </si>
+  <si>
+    <t>Geplante Maßnahme</t>
+  </si>
+  <si>
+    <t>Referenz auf eine geplante diagnostische Maßnahme – z. B. ServiceRequest.</t>
+  </si>
+  <si>
+    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  +The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
+  </si>
+  <si>
+    <t>Details in a form consistent with other applications and contexts of use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpl-3
+</t>
+  </si>
+  <si>
+    <t>{Request that resulted in Event in activity.actionResulting}</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail</t>
+  </si>
+  <si>
+    <t>In-line definition of activity</t>
+  </si>
+  <si>
+    <t>A simple summary of a planned activity suitable for a general care plan system (e.g. form driven) that doesn't know about specific resources such as procedure etc.</t>
+  </si>
+  <si>
+    <t>Details in a simple form for generic care plan systems.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.modifierExtension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.kind</t>
+  </si>
+  <si>
+    <t>Appointment | CommunicationRequest | DeviceRequest | MedicationRequest | NutritionOrder | Task | ServiceRequest | VisionPrescription</t>
+  </si>
+  <si>
+    <t>A description of the kind of resource the in-line definition of a care plan activity is representing.  The CarePlan.activity.detail is an in-line definition when a resource is not referenced using CarePlan.activity.reference.  For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest.</t>
+  </si>
+  <si>
+    <t>May determine what types of extensions are permitted.</t>
+  </si>
+  <si>
+    <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
+  </si>
+  <si>
+    <t>Allows Questionnaires that the patient (or practitioner) should fill in to fulfill the care plan activity.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.instantiatesUri</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.code</t>
+  </si>
+  <si>
+    <t>Detail type of activity</t>
+  </si>
+  <si>
+    <t>Detailed description of the type of planned activity; e.g. what lab test, what procedure, what kind of encounter.</t>
+  </si>
+  <si>
+    <t>Tends to be less relevant for activities involving particular products.  Codes should not convey negation - use "prohibited" instead.</t>
+  </si>
+  <si>
+    <t>Allows matching performed to planned as well as validation against protocols.</t>
+  </si>
+  <si>
+    <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.code</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>OBR-4 / RXE-2 / RXO-1 / RXD-2</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.reasonCode</t>
+  </si>
+  <si>
+    <t>Why activity should be done or why activity was prohibited</t>
+  </si>
+  <si>
+    <t>Provides the rationale that drove the inclusion of this particular activity as part of the plan or the reason why the activity was prohibited.</t>
+  </si>
+  <si>
+    <t>This could be a diagnosis code.  If a full condition record exists or additional detail is needed, use reasonCondition instead.</t>
+  </si>
+  <si>
+    <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.reasonCode</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.reasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Why activity is needed</t>
+  </si>
+  <si>
+    <t>Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
+  </si>
+  <si>
+    <t>Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.goal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(Goal|4.0.1)
 </t>
-  </si>
-  <si>
-    <t>Desired outcome of plan</t>
-  </si>
-  <si>
-    <t>Describes the intended objective(s) of carrying out the care plan.</t>
-  </si>
-  <si>
-    <t>Goal can be achieving a particular change or merely maintaining a current state or even slowing a decline.</t>
-  </si>
-  <si>
-    <t>Provides context for plan.  Allows plan effectiveness to be evaluated by clinicians.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode&lt;=OBJ].</t>
-  </si>
-  <si>
-    <t>GOL.1</t>
-  </si>
-  <si>
-    <t>CarePlan.activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Diagnostische Maßnahmen</t>
-  </si>
-  <si>
-    <t>Geplante bzw. durchgeführte Schritte des Diagnosepfads.</t>
-  </si>
-  <si>
-    <t>Allows systems to prompt for performance of planned activities, and validate plans against best practice.</t>
-  </si>
-  <si>
-    <t>cpl-3:Provide a reference or detail, not both {detail.empty() or reference.empty()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>{no mapping
-NOTE: This is a list of contained Request-Event tuples!}</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].target</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.id</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.outcomeCodeableConcept</t>
-  </si>
-  <si>
-    <t>Results of the activity</t>
-  </si>
-  <si>
-    <t>Identifies the outcome at the point when the status of the activity is assessed.  For example, the outcome of an education activity could be patient understands (or not).</t>
-  </si>
-  <si>
-    <t>Note that this should not duplicate the activity status (e.g. completed or in progress).</t>
-  </si>
-  <si>
-    <t>Identifies the results of the activity.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.outcomeReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DiagnosticReport|Observation|Procedure)
-</t>
-  </si>
-  <si>
-    <t>Ergebnis</t>
-  </si>
-  <si>
-    <t>Referenz auf das Ergebnis der Diagnostik – z. B. DiagnosticReport oder Observation.</t>
-  </si>
-  <si>
-    <t>The activity outcome is independent of the outcome of the related goal(s).  For example, if the goal is to achieve a target body weight of 150 lbs and an activity is defined to diet, then the activity outcome could be calories consumed whereas the goal outcome is an observation for the actual body weight measured.</t>
-  </si>
-  <si>
-    <t>Links plan to resulting actions.</t>
-  </si>
-  <si>
-    <t>{Event that is outcome of Request in activity.reference}</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=FLFS].source</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Comments about the activity status/progress</t>
-  </si>
-  <si>
-    <t>Notes about the adherence/status/progress of the activity.</t>
-  </si>
-  <si>
-    <t>This element should NOT be used to describe the activity to be performed - that occurs either within the resource pointed to by activity.detail.reference or in activity.detail.description.</t>
-  </si>
-  <si>
-    <t>Can be used to capture information about adherence, progress, concerns, etc.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
-  </si>
-  <si>
-    <t>NTE?</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(ServiceRequest|Appointment|Task)
-</t>
-  </si>
-  <si>
-    <t>Geplante Maßnahme</t>
-  </si>
-  <si>
-    <t>Referenz auf eine geplante diagnostische Maßnahme – z. B. ServiceRequest.</t>
-  </si>
-  <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  -The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
-  </si>
-  <si>
-    <t>Details in a form consistent with other applications and contexts of use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpl-3
-</t>
-  </si>
-  <si>
-    <t>{Request that resulted in Event in activity.actionResulting}</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail</t>
-  </si>
-  <si>
-    <t>In-line definition of activity</t>
-  </si>
-  <si>
-    <t>A simple summary of a planned activity suitable for a general care plan system (e.g. form driven) that doesn't know about specific resources such as procedure etc.</t>
-  </si>
-  <si>
-    <t>Details in a simple form for generic care plan systems.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.id</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.modifierExtension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.kind</t>
-  </si>
-  <si>
-    <t>Appointment | CommunicationRequest | DeviceRequest | MedicationRequest | NutritionOrder | Task | ServiceRequest | VisionPrescription</t>
-  </si>
-  <si>
-    <t>A description of the kind of resource the in-line definition of a care plan activity is representing.  The CarePlan.activity.detail is an in-line definition when a resource is not referenced using CarePlan.activity.reference.  For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest.</t>
-  </si>
-  <si>
-    <t>May determine what types of extensions are permitted.</t>
-  </si>
-  <si>
-    <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
-  </si>
-  <si>
-    <t>Allows Questionnaires that the patient (or practitioner) should fill in to fulfill the care plan activity.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.instantiatesUri</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.code</t>
-  </si>
-  <si>
-    <t>Detail type of activity</t>
-  </si>
-  <si>
-    <t>Detailed description of the type of planned activity; e.g. what lab test, what procedure, what kind of encounter.</t>
-  </si>
-  <si>
-    <t>Tends to be less relevant for activities involving particular products.  Codes should not convey negation - use "prohibited" instead.</t>
-  </si>
-  <si>
-    <t>Allows matching performed to planned as well as validation against protocols.</t>
-  </si>
-  <si>
-    <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.code</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>OBR-4 / RXE-2 / RXO-1 / RXD-2</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.reasonCode</t>
-  </si>
-  <si>
-    <t>Why activity should be done or why activity was prohibited</t>
-  </si>
-  <si>
-    <t>Provides the rationale that drove the inclusion of this particular activity as part of the plan or the reason why the activity was prohibited.</t>
-  </si>
-  <si>
-    <t>This could be a diagnosis code.  If a full condition record exists or additional detail is needed, use reasonCondition instead.</t>
-  </si>
-  <si>
-    <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.reasonCode</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Why activity is needed</t>
-  </si>
-  <si>
-    <t>Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
-  </si>
-  <si>
-    <t>Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.goal</t>
   </si>
   <si>
     <t>Goals this activity relates to</t>
@@ -4023,7 +4027,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>203</v>
       </c>
@@ -4042,7 +4046,7 @@
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>89</v>
@@ -5967,7 +5971,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>330</v>
       </c>
@@ -5986,7 +5990,7 @@
         <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
@@ -8173,17 +8177,17 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>331</v>
+        <v>427</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8261,10 +8265,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8290,16 +8294,16 @@
         <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8327,10 +8331,10 @@
         <v>196</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8348,7 +8352,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>88</v>
@@ -8363,24 +8367,24 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8406,13 +8410,13 @@
         <v>212</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8462,7 +8466,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8477,7 +8481,7 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
@@ -8491,10 +8495,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8517,70 +8521,70 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q58" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="R58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q58" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="R58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8595,10 +8599,10 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
@@ -8609,10 +8613,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8635,17 +8639,17 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8694,7 +8698,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8718,15 +8722,15 @@
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8749,19 +8753,19 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -8810,7 +8814,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8828,21 +8832,21 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8865,19 +8869,19 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -8926,7 +8930,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8941,24 +8945,24 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8981,13 +8985,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9017,10 +9021,10 @@
         <v>217</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9038,7 +9042,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9056,25 +9060,25 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9093,17 +9097,17 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9152,7 +9156,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9170,21 +9174,21 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9207,13 +9211,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9264,7 +9268,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9282,21 +9286,21 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9322,10 +9326,10 @@
         <v>222</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9376,7 +9380,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9394,7 +9398,7 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9405,10 +9409,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9434,14 +9438,14 @@
         <v>368</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9490,7 +9494,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9505,7 +9509,7 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>373</v>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
